--- a/output/SPX_daily_20260723.xlsx
+++ b/output/SPX_daily_20260723.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>-5.3</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>131.1</v>
+        <v>130.8</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="I11" s="16" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       </c>
       <c r="K11" s="18" t="inlineStr">
         <is>
-          <t>항공우주 및 방위산업 기업으로 기술 시스템 연구, 설계, 개발, 제조, 통합 및 유지 관리 사업을 영위합니다.</t>
+          <t>록히드 마틴은 항공우주 및 방위 기술 시스템의 연구, 개발, 제조 및 유지보수를 영위하는 기업입니다.</t>
         </is>
       </c>
       <c r="L11" s="18" t="inlineStr">
         <is>
-          <t>2분기 사상 최대 수주잔고 달성과 매출 및 이익 증가에 힘입어 연간 실적 가이던스를 상향 조정했습니다.</t>
+          <t>2분기 실적이 시장 예상치를 상회하고 연간 실적 가이던스를 상향 조정했다고 발표하면서 주가가 상승했습니다.</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="I12" s="16" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
-          <t>전 세계에 보안 제품 및 솔루션을 제공하는 기업입니다.</t>
+          <t>알레지온은 전 세계 고객을 대상으로 보안 제품 및 솔루션을 제공하는 기업입니다.</t>
         </is>
       </c>
       <c r="L12" s="18" t="inlineStr">
         <is>
-          <t>2분기 실적이 시장 예상치를 크게 상회하면서 주가가 상승했습니다.</t>
+          <t>2분기 실적이 시장 예상치를 크게 상회했다고 발표하면서 주가가 상승했습니다.</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>71.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="I13" s="16" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="K13" s="18" t="inlineStr">
         <is>
-          <t>미국, 캐나다, 유럽, 호주, 뉴질랜드에서 장비 대여 사업을 영위하는 기업입니다.</t>
+          <t>유나이티드 렌탈스는 미국 및 글로벌 시장에서 장비 대여 사업을 영위하는 기업입니다.</t>
         </is>
       </c>
       <c r="L13" s="18" t="inlineStr">
         <is>
-          <t>2분기 매출이 12% 증가하고 조정 EPS가 22% 상승하는 호실적을 달성하며 연간 가이던스를 상향했습니다.</t>
+          <t>2분기 매출과 조정 주당순이익이 증가한 호실적을 발표하고 2026년 연간 가이던스를 상향 조정함에 따라 주가가 상승했습니다.</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>써모 피셔 사이언티픽은 과학 연구 및 진단 솔루션을 제공하는 기업입니다.</t>
+          <t>써모 피셔 사이언티픽은 헬스케어 및 분석 관련 과학 제품과 서비스를 제공하는 기업입니다.</t>
         </is>
       </c>
       <c r="L14" s="18" t="inlineStr">
         <is>
-          <t>2분기 매출이 10% 증가했으며, 혁신과 전략적 인수를 바탕으로 연간 실적 가이던스를 상향 조정했습니다.</t>
+          <t>2분기 매출이 10% 증가하는 강세를 보이고 연간 실적 가이던스를 상향 조정함에 따라 주가가 상승했습니다.</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
-          <t>Quest Diagnostics는 미국에서 진단 검사 및 서비스를 제공합니다.</t>
+          <t>퀘스트 다이아그노스틱스는 미국에서 진단 검사 및 관련 서비스를 제공하는 기업입니다.</t>
         </is>
       </c>
       <c r="L15" s="18" t="inlineStr">
         <is>
-          <t>2분기 매출 성장을 기록하고 2026년 연간 실적 전망을 상향 조정했습니다.</t>
+          <t>2분기 두 자릿수 매출 성장을 기록하고 의사 및 병원 채널의 수요 증가에 힘입어 2026년 연간 실적 전망을 상향 조정하면서 주가가 상승했습니다.</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="I16" s="16" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
-          <t>다나허는 전 세계에 전문, 의료, 연구 및 산업용 제품과 서비스를 제공합니다.</t>
+          <t>다나허는 미국, 중국 및 전 세계에서 전문, 의료, 연구 및 산업용 제품과 서비스를 설계, 제조 및 판매합니다.</t>
         </is>
       </c>
       <c r="L16" s="18" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
-          <t>RTX는 항공우주 및 방산 기업으로 전 세계 고객에게 시스템과 서비스를 제공합니다.</t>
+          <t>RTX는 전 세계 상업, 군사 및 정부 고객을 대상으로 시스템과 서비스를 제공하는 항공우주 및 방산 기업입니다.</t>
         </is>
       </c>
       <c r="L17" s="18" t="inlineStr">
         <is>
-          <t>2분기 매출이 14% 증가하는 등 시장 예상치를 웃돈 실적을 발표하고 연간 전망을 상향 조정했습니다.</t>
+          <t>예상치를 상회하는 2분기 실적을 발표하고 수주 잔고 증가와 견조한 수요에 힘입어 연간 매출 가이던스를 상향 조정한 것이 주가 상승을 이끌었습니다.</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>98.09999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="I18" s="16" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="K18" s="18" t="inlineStr">
         <is>
-          <t>CSX는 미국과 캐나다에서 철도 기반 화물 운송 서비스를 제공합니다.</t>
+          <t>CSX는 미국과 캐나다에서 철도 기반 화물 수송 서비스를 제공하는 기업입니다.</t>
         </is>
       </c>
       <c r="L18" s="18" t="inlineStr">
         <is>
-          <t>시장 예상치를 상회하는 2분기 실적을 발표한 것이 호재로 작용했습니다.</t>
+          <t>2분기 매출이 전년 대비 10.1% 증가한 39.4억 달러를 기록하고 주당순이익이 시장 예상치를 상회하는 호실적을 발표하면서 주가가 상승했습니다.</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="K19" s="18" t="inlineStr">
         <is>
-          <t>허니웰 인터내셔널은 다각화된 글로벌 기술 및 제조 서비스를 제공합니다.</t>
+          <t>하니웰 인터내셔널은 산업 및 기술 솔루션을 제공하는 다각화된 글로벌 기업입니다.</t>
         </is>
       </c>
       <c r="L19" s="18" t="inlineStr">
         <is>
-          <t>2분기 4%의 자체 매출 성장과 마진 확대를 기록하고 연간 실적 가이던스를 대폭 상향 조정하면서 주가가 상승했습니다.</t>
+          <t>견조한 2분기 실적 발표와 함께 연간 실적 가이던스를 대폭 상향 조정한 점이 주가 상승을 이끌었습니다.</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>35.8</v>
+        <v>35.1</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I20" s="16" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="K20" s="18" t="inlineStr">
         <is>
-          <t>로퍼 테크놀로지는 다양한 산업 및 기술 솔루션을 제공하는 기업입니다.</t>
+          <t>로퍼 테크놀로지는 다양한 산업을 위한 소프트웨어 및 기술 솔루션을 제공하는 기업입니다.</t>
         </is>
       </c>
       <c r="L20" s="18" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="K21" s="18" t="inlineStr">
         <is>
-          <t>노퍽 서던은 미국 내 원자재, 중간재, 완제품의 철도 운송 서비스를 제공합니다.</t>
+          <t>노퍽 서던은 미국 내 원자재, 중간재 및 완제품의 철도 수송 사업을 영위합니다.</t>
         </is>
       </c>
       <c r="L21" s="18" t="inlineStr">
         <is>
-          <t>화물 물동량 회복과 수요 증가에 힘입어 2분기 순이익이 7% 증가하는 등 시장 예상치를 상회하는 실적을 발표했습니다.</t>
+          <t>화물 물동량 회복에 힘입어 시장 예상치를 상회하는 2분기 실적과 7%의 순이익 성장을 발표하며 주가가 상승했습니다.</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="I22" s="16" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="K22" s="18" t="inlineStr">
         <is>
-          <t>L3해리스 테크놀로지는 첨단 방산 및 항공우주 기술 솔루션을 제공합니다.</t>
+          <t>L3해리스 테크놀로지는 항공우주 및 방위 산업용 기술 솔루션을 제공하는 기업입니다.</t>
         </is>
       </c>
       <c r="L22" s="18" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="K23" s="18" t="inlineStr">
         <is>
-          <t>찰스 리버 레이보러토리스 인터내셔널은 생명과학 분야 연구 제품과 서비스를 제공하는 기업입니다.</t>
+          <t>찰스리버 레이보러토리스는 임상 전 제약 및 바이오 제품 개발 서비스를 제공하는 기업입니다.</t>
         </is>
       </c>
       <c r="L23" s="18" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -1641,30 +1641,30 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="D24" s="13" t="n">
-        <v>39.5</v>
+        <v>274.6</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
           <t>+4.7</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>+2.7</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>+10.5</t>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="H24" s="15" t="inlineStr">
@@ -1673,21 +1673,21 @@
         </is>
       </c>
       <c r="I24" s="16" t="n">
-        <v>270</v>
+        <v>44</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>애질런트 테크놀로지는 생명과학, 진단 및 응용 화학 분야에 통합 솔루션을 제공하는 기업입니다.</t>
+          <t>GE 버노바는 전력 생산, 송전, 변환 및 저장 관련 제품과 서비스를 제공하는 에너지 기업입니다.</t>
         </is>
       </c>
       <c r="L24" s="18" t="inlineStr">
         <is>
-          <t>난소암, 나팔관암, 원발성 복막암 환자 식별을 위한 동반 진단 기기 PD-L1 IHC 22C3 pharmDx의 유럽연합(EU) 승인을 획득했다고 발표한 후 주가가 상승했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -1697,30 +1697,30 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>274.6</v>
+        <v>39.5</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
           <t>+4.7</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>-0.4</t>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>+2.7</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>+10.5</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="I25" s="16" t="n">
-        <v>44</v>
+        <v>271</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K25" s="18" t="inlineStr">
         <is>
-          <t>GE 버노바는 전력 생산, 송전, 변환 및 저장과 관련된 솔루션을 제공하는 에너지 기업입니다.</t>
+          <t>애질런트 테크놀로지는 생명과학, 진단 및 응용 화학 분야의 분석 측정 솔루션을 제공하는 기업입니다.</t>
         </is>
       </c>
       <c r="L25" s="18" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>상피성 난소암 등의 키트루다 치료 적격성을 확인하는 동반 진단 기기 'PD-L1 IHC 22C3 pharmDx'가 유럽연합(EU) 인증을 획득했다고 발표했습니다.</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
-          <t>아이큐비아 홀딩스는 의료 및 생명과학 산업에 데이터 및 임상 연구 솔루션을 제공하는 기업입니다.</t>
+          <t>아이큐비아 홀딩스는 의료 정보 기술 및 임상 연구 관련 솔루션을 제공하는 기업입니다.</t>
         </is>
       </c>
       <c r="L26" s="18" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
-          <t>자회사를 통해 미국에서 철도 운송 사업을 영위하고 있습니다.</t>
+          <t>자회사 유니온 퍼시픽 철도 회사를 통해 미국에서 철도 사업을 운영합니다.</t>
         </is>
       </c>
       <c r="L27" s="18" t="inlineStr">
         <is>
-          <t>2026년 2분기 영업수익이 12% 증가하는 등 호실적을 기록하고 재무 전망을 상향 조정한 영향입니다.</t>
+          <t>2026년 2분기 영업 수익이 12% 증가했다고 발표하고 효율성 향상에 힘입어 실적 호조를 기록한 점이 주가 상승을 이끌었습니다.</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
-          <t>기술 및 소프트웨어 기업으로서 전 세계 고객에게 다양한 솔루션을 제공합니다.</t>
+          <t>기술 및 소프트웨어 기업으로서 글로벌 시장에 다양한 솔루션을 제공합니다.</t>
         </is>
       </c>
       <c r="L28" s="18" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="K29" s="18" t="inlineStr">
         <is>
-          <t>페덱스 프레이트 홀딩스는 화물 운송 관련 사업을 영위하는 기업입니다.</t>
+          <t>페덱스 프레이트 홀딩스는 화물 운송 서비스를 제공하는 지주회사입니다.</t>
         </is>
       </c>
       <c r="L29" s="18" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="K30" s="18" t="inlineStr">
         <is>
-          <t>메틀러 토레도 인터내셔널은 정밀 계량 및 분석 기기를 제공하는 기업입니다.</t>
+          <t>메틀러 토레도 인터내셔널은 정밀 기기 및 정밀 측정 장비를 제공합니다.</t>
         </is>
       </c>
       <c r="L30" s="18" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="D32" s="24" t="n">
-        <v>1200.7</v>
+        <v>1262.6</v>
       </c>
       <c r="E32" s="25" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="L32" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D33" s="24" t="n">
-        <v>184.4</v>
+        <v>182.8</v>
       </c>
       <c r="E33" s="25" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="I33" s="27" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J33" s="28" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="L33" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="L34" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="L35" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="D36" s="24" t="n">
-        <v>3876.6</v>
+        <v>3885.3</v>
       </c>
       <c r="E36" s="25" t="inlineStr">
         <is>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="K36" s="29" t="inlineStr">
         <is>
-          <t>통신·미디어·인터넷 서비스 분야를 영위하는 미국 상장 기업</t>
+          <t>알파벳은 구글 등을 보유한 글로벌 기술 및 미디어 지주회사입니다.</t>
         </is>
       </c>
       <c r="L36" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>실적 발표에서 대규모 AI 투자 및 지출 확대에 따른 현금 흐름 우려가 제기되면서 주가가 하락했습니다.</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2368,12 @@
       </c>
       <c r="K37" s="29" t="inlineStr">
         <is>
-          <t>금융 분야를 영위하는 미국 상장 기업</t>
+          <t>자회사를 통해 미국의 중하위 및 중산층 가정을 대상으로 생명 및 보조 건강 보험 상품을 제공합니다.</t>
         </is>
       </c>
       <c r="L37" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>2분기 실적이 시장 예상치에 부합했으나 투자자들의 기대를 충족시키지 못하면서 주가가 하락했습니다.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="D38" s="24" t="n">
-        <v>3884.6</v>
+        <v>3893.3</v>
       </c>
       <c r="E38" s="25" t="inlineStr">
         <is>
@@ -2424,12 +2424,12 @@
       </c>
       <c r="K38" s="29" t="inlineStr">
         <is>
-          <t>통신·미디어·인터넷 서비스 분야를 영위하는 미국 상장 기업</t>
+          <t>알파벳은 구글 등을 보유한 글로벌 기술 및 미디어 지주회사입니다.</t>
         </is>
       </c>
       <c r="L38" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>실적 발표에서 대규모 AI 투자 및 지출 확대에 따른 현금 흐름 우려가 제기되면서 주가가 하락했습니다.</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="K39" s="29" t="inlineStr">
         <is>
-          <t>통신·미디어·인터넷 서비스 분야를 영위하는 미국 상장 기업</t>
+          <t>컴캐스트는 전 세계에서 미디어 및 기술 서비스를 제공하는 글로벌 기업입니다.</t>
         </is>
       </c>
       <c r="L39" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>2분기 실적 발표에서 미디어 호조에도 불구하고 초고속 인터넷 가입자 감소세 지속과 테마파크 부문의 어려움이 부각되었습니다.</t>
         </is>
       </c>
     </row>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="K40" s="29" t="inlineStr">
         <is>
-          <t>사우스웨스트 항공은 미국의 여객 항공 운송 서비스를 제공하는 항공사입니다.</t>
+          <t>사우스웨스트 항공은 고객에게 항공 여객 운송 서비스를 제공하는 항공사입니다.</t>
         </is>
       </c>
       <c r="L40" s="29" t="inlineStr">
         <is>
-          <t>2분기 기록적인 매출과 조정 EPS 120% 증가를 발표했으나, 높은 연료 가격과 경쟁 압력으로 인한 도전 과제가 함께 부각되었습니다.</t>
+          <t>2분기 실적 발표에서 조정 EPS가 120% 증가하고 분기 매출 최기록을 달성했으나, 상승한 연료 가격과 경쟁 압력 등 경영 과제가 함께 지목되었습니다.</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="K41" s="29" t="inlineStr">
         <is>
-          <t>데커스 아웃도어는 캐주얼 및 고성능 신발, 의류, 액세서리를 디자인 및 유통합니다.</t>
+          <t>데커스 아웃도어는 캐주얼 및 고성능 라이프스타일용 신발, 의류, 액세서리를 디자인하고 유통합니다.</t>
         </is>
       </c>
       <c r="L41" s="29" t="inlineStr">
         <is>
-          <t>1분기 실적 발표에서 EPS 예상치를 상회하고 연간 이익 전망을 올렸으나, 연간 매출 전망이 월가 기대치에 미치지 못해 주가가 하락했습니다.</t>
+          <t>2027 회계연도 1분기 매출이 호카 및 어그 브랜드의 성장과 직판 매출 호조에 힘입어 회사 역사상 최초로 10억 달러를 돌파했다고 발표했습니다.</t>
         </is>
       </c>
     </row>
@@ -2648,12 +2648,12 @@
       </c>
       <c r="K42" s="29" t="inlineStr">
         <is>
-          <t>허니웰 에어로스페이스는 항공우주 관련 제품과 기술 솔루션을 제공하는 기업입니다.</t>
+          <t>허니웰 에어로스페이스는 항공우주 관련 기술 및 제품 서비스를 제공하는 기업입니다.</t>
         </is>
       </c>
       <c r="L42" s="29" t="inlineStr">
         <is>
-          <t>2분기 실적 발표 이후 연간 조정 EPS 전망치는 상향 조정했으나, 매출 전망을 하향 조정한 점이 주가에 부담으로 작용했습니다.</t>
+          <t>2분기 실적 발표 후 2026년 조정 EPS 가이던스를 상향 조정했으나, 매출 전망치를 하향 조정했다고 밝혔습니다.</t>
         </is>
       </c>
     </row>
@@ -2704,12 +2704,12 @@
       </c>
       <c r="K43" s="29" t="inlineStr">
         <is>
-          <t>아카마이 테크놀로지는 클라우드 서비스 및 콘텐츠 전송 네트워크 솔루션을 제공합니다.</t>
+          <t>아카마이 테크놀로지는 콘텐츠 전송 및 클라우드 솔루션을 제공하는 글로벌 정보기술 기업입니다.</t>
         </is>
       </c>
       <c r="L43" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="D44" s="24" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="E44" s="25" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="I44" s="27" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J44" s="28" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="K44" s="29" t="inlineStr">
         <is>
-          <t>상업, 소비자 및 주택담보대출 금융 서비스를 제공하는 헌팅턴 내셔널 은행의 지주회사입니다.</t>
+          <t>헌팅턴 뱅크스셰어스는 상업, 소비자 및 주택담보대출 금융 서비스를 제공하는 은행 지주회사입니다.</t>
         </is>
       </c>
       <c r="L44" s="29" t="inlineStr">
         <is>
-          <t>예금 비용 상승과 약화된 순이자이익(NII) 가이던스에 대한 우려가 주된 요인으로 지목되었습니다.</t>
+          <t>예금 비용 상승과 약화된 순이자이익 가이던스에 대한 우려가 제기된 한편, 경영진은 하반기 실적 반등을 전망했습니다.</t>
         </is>
       </c>
     </row>
@@ -2775,16 +2775,16 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>Oracle Corporation</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D45" s="24" t="n">
-        <v>345.8</v>
+        <v>2513.5</v>
       </c>
       <c r="E45" s="25" t="inlineStr">
         <is>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>-27.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="H45" s="26" t="inlineStr">
@@ -2807,21 +2807,21 @@
         </is>
       </c>
       <c r="I45" s="27" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="J45" s="28" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K45" s="29" t="inlineStr">
         <is>
-          <t>전 세계 기업용 정보 기술 프레임워크 구축 및 지원 제품과 서비스를 제공합니다.</t>
+          <t>아마존은 전자상거래 및 클라우드 서비스 등을 제공하는 글로벌 기업입니다.</t>
         </is>
       </c>
       <c r="L45" s="29" t="inlineStr">
         <is>
-          <t>미국 국방부로부터 최대 69억 9,000만 달러 규모의 10년 만기 엔터프라이즈 소프트웨어 계약을 수주했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -2831,16 +2831,16 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="D46" s="24" t="n">
-        <v>2513.5</v>
+        <v>345.8</v>
       </c>
       <c r="E46" s="25" t="inlineStr">
         <is>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-27.1</t>
         </is>
       </c>
       <c r="H46" s="26" t="inlineStr">
@@ -2863,21 +2863,21 @@
         </is>
       </c>
       <c r="I46" s="27" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J46" s="28" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K46" s="29" t="inlineStr">
         <is>
-          <t>전자상거래 및 클라우드 컴퓨팅 서비스를 제공하는 글로벌 테크 기업입니다.</t>
+          <t>오라클은 전 세계 기업용 정보기술 프레임워크 구축 및 지원 제품과 서비스를 제공합니다.</t>
         </is>
       </c>
       <c r="L46" s="29" t="inlineStr">
         <is>
-          <t>중국 영향력 관련 상원 조사와 FTC와의 25억 달러 합의, AI 비용 우려가 주가 하락 원인으로 지목되었습니다.</t>
+          <t>미국 전쟁부로부터 최대 69억 9,000만 달러 규모의 10년 단위 기업 소프트웨어 및 클라우드 서비스 공급 계약을 수주했습니다.</t>
         </is>
       </c>
     </row>
@@ -2928,12 +2928,12 @@
       </c>
       <c r="K47" s="29" t="inlineStr">
         <is>
-          <t>가맹점, 소비자, 배달원을 연결하는 커머스 플랫폼을 운영합니다.</t>
+          <t>도어대시는 가맹점, 소비자, 배달원을 연결하는 커머스 플랫폼을 운영합니다.</t>
         </is>
       </c>
       <c r="L47" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="L48" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L49" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -3055,30 +3055,30 @@
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="D50" s="24" t="n">
-        <v>44.2</v>
+        <v>9.1</v>
       </c>
       <c r="E50" s="25" t="inlineStr">
         <is>
           <t>-4.3</t>
         </is>
       </c>
-      <c r="F50" s="25" t="inlineStr">
-        <is>
-          <t>-0.4</t>
+      <c r="F50" s="30" t="inlineStr">
+        <is>
+          <t>+4.9</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>-12.8</t>
+          <t>-17.7</t>
         </is>
       </c>
       <c r="H50" s="26" t="inlineStr">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="I50" s="27" t="n">
-        <v>249</v>
+        <v>494</v>
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="L50" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -3111,30 +3111,30 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="D51" s="24" t="n">
-        <v>9.1</v>
+        <v>44.2</v>
       </c>
       <c r="E51" s="25" t="inlineStr">
         <is>
           <t>-4.3</t>
         </is>
       </c>
-      <c r="F51" s="30" t="inlineStr">
-        <is>
-          <t>+4.9</t>
+      <c r="F51" s="25" t="inlineStr">
+        <is>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>-17.7</t>
+          <t>-12.8</t>
         </is>
       </c>
       <c r="H51" s="26" t="inlineStr">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="I51" s="27" t="n">
-        <v>494</v>
+        <v>250</v>
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
@@ -3157,23 +3157,24 @@
       </c>
       <c r="L51" s="29" t="inlineStr">
         <is>
-          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+          <t>최근 한 달 내 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
-          <t>📈 금일 시황 요약 — 하락 종목이 다소 우세한 약한 위험 회피 흐름</t>
+          <t>📈 금일 시황 요약 — 빅테크 현금 소진 우려와 유가 상승 속 하락 우세 시장 흐름</t>
         </is>
       </c>
     </row>
     <row r="55" ht="82" customHeight="1">
       <c r="A55" s="32" t="inlineStr">
         <is>
-          <t>관측: 전체 495개 종목 중 상승 209개(42%), 하락 286개로 하락 비율이 높았습니다. 강세 섹터는 Industrials +1.8%, Health Care +1.4%였으며, 약세 섹터는 Communication Services -5.9%, Consumer Discretionary -5.3%를 기록했습니다. 개별 종목 중 LMT가 +10.5%로 가장 큰 상승을 보였고, TSLA는 -14.5%로 가장 큰 하락을 보였습니다.
-해석: 당일 전후 시황 기사 3건 이상을 검증하지 못했습니다. 아래 해석은 가격·시장 폭·섹터 수익률에 한정됩니다.
-유의: NVIDIA NIM GPT-OSS 120B가 가격·시장 폭·섹터 수익률만 정리한 자동 요약이며 뉴스 근거 기반 해석이나 투자 조언이 아닙니다.</t>
+          <t>관측: 상승 209개, 하락 286개로 상승 비율 42%를 기록하며 하락 종목이 다소 우세를 보였습니다. 섹터별로는 산업재(+1.8%)와 헬스케어(+1.4%)가 강세를 나타낸 반면, 커뮤니케이션 서비스(-5.9%)와 경기소비재(-5.4%)는 약세를 보였습니다. 개별 종목 중에서는 LMT(+10.5%)가 가장 큰 폭으로 상승했고, 매출은 예상을 상회했으나 순이익이 시장 전망에 미달한 TSLA(-14.5%)가 가장 큰 하락 폭을 기록했습니다. 주요 보도에 따르면 빅테크의 현금 소진 우려로 주가가 하락하고 유가가 100달러를 돌파했으며, 미-이란 갈등에 따른 유가 상승과 미 국채 수익률 상승, ECB의 에너지 가격 상승 및 인플레이션 우려가 관측되었습니다.
+해석: 빅테크 기업들의 현금 소진 우려와 테슬라 등 주요 기업의 실적 이슈, 유가 100달러 돌파 및 인플레이션 지속 전망 등 악재가 겹치며 경기소비재와 커뮤니케이션 서비스 섹터를 중심으로 매도 압력이 나타났습니다. 다만 산업재 및 헬스케어 섹터와 방어적 종목군이 상승세를 나타내며 일방적인 시장 전체 하락보다는 약한 위험회피 양상을 보여주었습니다.
+근거 기사: Traders see September rate hike as European Central Bank mulls energy price spik (https://www.cnbc.com/2026/07/23/interest-rate-hike-iran-european-central-bank.html) | Jim Cramer's top 10 things to watch in the stock market Thursday (https://www.cnbc.com/2026/07/23/jim-cramers-top-10-things-to-watch-in-the-stock-market-thursday.html) | Wall St ends higher on chip stocks recovery; earnings in focus - Reuters (https://news.google.com/rss/articles/CBMiowFBVV95cUxOUDZOb0lyeDNtSHo4bVQ4MlJ3RnhPUUR2WmxYT2xqaWRVNFFVNkNUdHBNUUIxWm5kZGpVaVc0SFZicnBmN1F0RWI3RXpqNUpCbjQ3RHhPZEJkTmlaeGI3YXp3MUlSSXN2RGdBZ3dfekVaQzQxbFJzeHhuNU9veGtKMzdidFZ1N2QwbFE3Z3B1VmxoY1VuTUFtU3Rfa09XMlRMWl9B?oc=5) | Stocks sink on Big Tech cash burn; oil hits $100 for first time since May - Reut (https://news.google.com/rss/articles/CBMie0FVX3lxTE01ZXA2WXo2VDZMLUZycUVJVDJ3bTlRSnpyUFg0VnRDUkU1OGVtNGVwQTlSYWgwbjlRRE1NS3RJWE0xTlJrekNsZnJEeHAyZlpGSkJCM2R5LU5uMmFTY2gtS3dmVHBhMGRnZ083S3pycEl0OS1jd2g5SngxQQ?oc=5) | Yen slides past 163 mark to fresh 40-year low against US dollar (https://www.bloomberg.com/news/articles/2026-07-21/yen-slides-past-163-mark-to-fresh-four-decade-low-against-dollar)
+유의: Gemini + Finnhub가 코드가 선정한 Finnhub 기사 5건과 시장 수치를 바탕으로 작성한 자동 요약이며 투자 조언이 아닙니다.</t>
         </is>
       </c>
     </row>
